--- a/docs/Decodifiche/141_dmnm_dec_tipo_comune.xlsx
+++ b/docs/Decodifiche/141_dmnm_dec_tipo_comune.xlsx
@@ -35,7 +35,7 @@
     <t>Stesso comune di morte</t>
   </si>
   <si>
-    <t>2025-12-02 20:14:36.0</t>
+    <t>2025-12-04 11:48:12.0</t>
   </si>
   <si>
     <t>9999-12-31 00:00:00.0</t>
